--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250501_20251101.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250501_20251101.xlsx
@@ -701,37 +701,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55.55555555555556</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="C7" t="n">
-        <v>44.44444444444444</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="D7" t="n">
-        <v>142.7018254859107</v>
+        <v>46.1337095223199</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>INE0NT901020</t>
+          <t>INE158A01026</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>-11.11111111111111</v>
+        <v>-14.28571428571428</v>
       </c>
       <c r="H7" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
         <v>35</v>
       </c>
       <c r="J7" t="n">
-        <v>4037.8</v>
+        <v>5544</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -745,37 +745,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57.14285714285714</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="C8" t="n">
-        <v>42.85714285714285</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="D8" t="n">
-        <v>46.1337095223199</v>
+        <v>142.7018254859107</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>INE158A01026</t>
+          <t>INE0NT901020</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>-14.28571428571428</v>
+        <v>-11.11111111111111</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="I8" t="n">
         <v>35</v>
       </c>
       <c r="J8" t="n">
-        <v>5544</v>
+        <v>4037.8</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>-12.6984126984127</v>
@@ -1080,7 +1080,7 @@
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J15" t="n">
         <v>1928.9</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
         <v>-15.87301587301588</v>
@@ -1168,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J17" t="n">
         <v>847.85</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
         <v>-11.11111111111111</v>
@@ -1256,7 +1256,7 @@
         <v>32</v>
       </c>
       <c r="I19" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J19" t="n">
         <v>2438.7</v>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
         <v>-11.11111111111111</v>
@@ -1300,7 +1300,7 @@
         <v>27</v>
       </c>
       <c r="I20" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J20" t="n">
         <v>136.99</v>
